--- a/Server/Received_data/Statistics/2024/Documents/Статистика без выбросов за 2024 год.xlsx
+++ b/Server/Received_data/Statistics/2024/Documents/Статистика без выбросов за 2024 год.xlsx
@@ -663,7 +663,7 @@
         <v>58</v>
       </c>
       <c r="M4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N4" t="n">
         <v>5</v>
@@ -722,7 +722,7 @@
         <v>3.885482758620689</v>
       </c>
       <c r="M5" t="n">
-        <v>9.843571428571428</v>
+        <v>10.484375</v>
       </c>
       <c r="N5" t="n">
         <v>3.876600000000001</v>
@@ -779,7 +779,7 @@
         <v>0.9748339173234517</v>
       </c>
       <c r="M6" t="n">
-        <v>2.741788823447378</v>
+        <v>3.119058279925438</v>
       </c>
       <c r="N6" t="n">
         <v>0.1910622935065943</v>
@@ -897,7 +897,7 @@
         <v>3.129</v>
       </c>
       <c r="M8" t="n">
-        <v>7.8375</v>
+        <v>8.28875</v>
       </c>
       <c r="N8" t="n">
         <v>3.806</v>
@@ -956,7 +956,7 @@
         <v>3.7055</v>
       </c>
       <c r="M9" t="n">
-        <v>10.34</v>
+        <v>10.495</v>
       </c>
       <c r="N9" t="n">
         <v>3.861</v>
@@ -1015,7 +1015,7 @@
         <v>4.51075</v>
       </c>
       <c r="M10" t="n">
-        <v>11.495</v>
+        <v>12.6825</v>
       </c>
       <c r="N10" t="n">
         <v>3.984</v>
@@ -1074,7 +1074,7 @@
         <v>7.512</v>
       </c>
       <c r="M11" t="n">
-        <v>13.71</v>
+        <v>14.97</v>
       </c>
       <c r="N11" t="n">
         <v>4.12</v>
@@ -1137,7 +1137,7 @@
         <v>58</v>
       </c>
       <c r="M12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N12" t="n">
         <v>5</v>
@@ -1196,7 +1196,7 @@
         <v>0.6596458620689655</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1443114285714286</v>
+        <v>0.2351725</v>
       </c>
       <c r="N13" t="n">
         <v>0.4582999999999999</v>
@@ -1253,7 +1253,7 @@
         <v>0.4066532036369456</v>
       </c>
       <c r="M14" t="n">
-        <v>0.06390801786645434</v>
+        <v>0.2637169828623102</v>
       </c>
       <c r="N14" t="n">
         <v>0.06993854445153974</v>
@@ -1371,7 +1371,7 @@
         <v>0.134925</v>
       </c>
       <c r="M16" t="n">
-        <v>0.09242499999999999</v>
+        <v>0.1018125</v>
       </c>
       <c r="N16" t="n">
         <v>0.4165</v>
@@ -1430,7 +1430,7 @@
         <v>0.8342000000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>0.152</v>
+        <v>0.1651</v>
       </c>
       <c r="N17" t="n">
         <v>0.4808</v>
@@ -1489,7 +1489,7 @@
         <v>1.0205</v>
       </c>
       <c r="M18" t="n">
-        <v>0.18255</v>
+        <v>0.2005</v>
       </c>
       <c r="N18" t="n">
         <v>0.4922</v>
@@ -1548,7 +1548,7 @@
         <v>1.181</v>
       </c>
       <c r="M19" t="n">
-        <v>0.2413</v>
+        <v>0.8712</v>
       </c>
       <c r="N19" t="n">
         <v>0.5406</v>
@@ -1611,7 +1611,7 @@
         <v>58</v>
       </c>
       <c r="M20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N20" t="n">
         <v>5</v>
@@ -1670,7 +1670,7 @@
         <v>18.839</v>
       </c>
       <c r="M21" t="n">
-        <v>18.58671428571429</v>
+        <v>24.383375</v>
       </c>
       <c r="N21" t="n">
         <v>22.688</v>
@@ -1727,7 +1727,7 @@
         <v>6.656485277202529</v>
       </c>
       <c r="M22" t="n">
-        <v>16.70483667199698</v>
+        <v>22.53879459913823</v>
       </c>
       <c r="N22" t="n">
         <v>1.858163071422957</v>
@@ -1845,7 +1845,7 @@
         <v>12.26</v>
       </c>
       <c r="M24" t="n">
-        <v>4.7615</v>
+        <v>4.80325</v>
       </c>
       <c r="N24" t="n">
         <v>21.18</v>
@@ -1904,7 +1904,7 @@
         <v>20.88</v>
       </c>
       <c r="M25" t="n">
-        <v>17.87</v>
+        <v>19.59</v>
       </c>
       <c r="N25" t="n">
         <v>23.11</v>
@@ -1963,7 +1963,7 @@
         <v>24.385</v>
       </c>
       <c r="M26" t="n">
-        <v>24.545</v>
+        <v>33.305</v>
       </c>
       <c r="N26" t="n">
         <v>24.08</v>
@@ -2022,7 +2022,7 @@
         <v>28.62</v>
       </c>
       <c r="M27" t="n">
-        <v>49.88</v>
+        <v>64.95999999999999</v>
       </c>
       <c r="N27" t="n">
         <v>24.7</v>
@@ -2085,7 +2085,7 @@
         <v>58</v>
       </c>
       <c r="M28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N28" t="n">
         <v>5</v>
@@ -2144,7 +2144,7 @@
         <v>3.485418965517241</v>
       </c>
       <c r="M29" t="n">
-        <v>2.0503</v>
+        <v>1.9616375</v>
       </c>
       <c r="N29" t="n">
         <v>2.0338</v>
@@ -2201,7 +2201,7 @@
         <v>2.476202872286865</v>
       </c>
       <c r="M30" t="n">
-        <v>2.11949277422689</v>
+        <v>1.978228496795988</v>
       </c>
       <c r="N30" t="n">
         <v>0.3670697481405952</v>
@@ -2319,7 +2319,7 @@
         <v>1.0775</v>
       </c>
       <c r="M32" t="n">
-        <v>0.38745</v>
+        <v>0.393825</v>
       </c>
       <c r="N32" t="n">
         <v>1.73</v>
@@ -2378,7 +2378,7 @@
         <v>3.5665</v>
       </c>
       <c r="M33" t="n">
-        <v>0.4121</v>
+        <v>0.8765499999999999</v>
       </c>
       <c r="N33" t="n">
         <v>2.189</v>
@@ -2437,7 +2437,7 @@
         <v>4.46775</v>
       </c>
       <c r="M34" t="n">
-        <v>3.935</v>
+        <v>3.872</v>
       </c>
       <c r="N34" t="n">
         <v>2.27</v>
@@ -2559,7 +2559,7 @@
         <v>58</v>
       </c>
       <c r="M36" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N36" t="n">
         <v>5</v>
@@ -2618,7 +2618,7 @@
         <v>4.732655172413793</v>
       </c>
       <c r="M37" t="n">
-        <v>13.41028571428572</v>
+        <v>13.43275</v>
       </c>
       <c r="N37" t="n">
         <v>3.4438</v>
@@ -2675,7 +2675,7 @@
         <v>0.5917005985345207</v>
       </c>
       <c r="M38" t="n">
-        <v>5.397869385670785</v>
+        <v>4.997859877701941</v>
       </c>
       <c r="N38" t="n">
         <v>0.08582074341323305</v>
@@ -2793,7 +2793,7 @@
         <v>4.32175</v>
       </c>
       <c r="M40" t="n">
-        <v>9.870999999999999</v>
+        <v>11.6555</v>
       </c>
       <c r="N40" t="n">
         <v>3.422</v>
@@ -2852,7 +2852,7 @@
         <v>4.613</v>
       </c>
       <c r="M41" t="n">
-        <v>13.83</v>
+        <v>13.71</v>
       </c>
       <c r="N41" t="n">
         <v>3.449</v>
@@ -2911,7 +2911,7 @@
         <v>5.1725</v>
       </c>
       <c r="M42" t="n">
-        <v>17.055</v>
+        <v>16.7225</v>
       </c>
       <c r="N42" t="n">
         <v>3.456</v>
@@ -3033,7 +3033,7 @@
         <v>58</v>
       </c>
       <c r="M44" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N44" t="n">
         <v>5</v>
@@ -3092,7 +3092,7 @@
         <v>2.362413793103448</v>
       </c>
       <c r="M45" t="n">
-        <v>4.581857142857143</v>
+        <v>4.612500000000001</v>
       </c>
       <c r="N45" t="n">
         <v>0.41026</v>
@@ -3149,7 +3149,7 @@
         <v>0.3148751372959039</v>
       </c>
       <c r="M46" t="n">
-        <v>0.9627528981297033</v>
+        <v>0.8955399010014653</v>
       </c>
       <c r="N46" t="n">
         <v>0.06877632586871736</v>
@@ -3267,7 +3267,7 @@
         <v>2.1435</v>
       </c>
       <c r="M48" t="n">
-        <v>4.0305</v>
+        <v>4.34725</v>
       </c>
       <c r="N48" t="n">
         <v>0.3552</v>
@@ -3326,7 +3326,7 @@
         <v>2.3955</v>
       </c>
       <c r="M49" t="n">
-        <v>5.092</v>
+        <v>4.9595</v>
       </c>
       <c r="N49" t="n">
         <v>0.4333</v>
@@ -3385,7 +3385,7 @@
         <v>2.572</v>
       </c>
       <c r="M50" t="n">
-        <v>5.173500000000001</v>
+        <v>5.14325</v>
       </c>
       <c r="N50" t="n">
         <v>0.4345</v>
@@ -3507,7 +3507,7 @@
         <v>58</v>
       </c>
       <c r="M52" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N52" t="n">
         <v>5</v>
@@ -3566,7 +3566,7 @@
         <v>1.559103448275862</v>
       </c>
       <c r="M53" t="n">
-        <v>2.441142857142857</v>
+        <v>2.413625</v>
       </c>
       <c r="N53" t="n">
         <v>1.1388</v>
@@ -3623,7 +3623,7 @@
         <v>0.1099552843173273</v>
       </c>
       <c r="M54" t="n">
-        <v>0.5645123053195057</v>
+        <v>0.5284005346325834</v>
       </c>
       <c r="N54" t="n">
         <v>0.03371498183300708</v>
@@ -3741,7 +3741,7 @@
         <v>1.473</v>
       </c>
       <c r="M56" t="n">
-        <v>2.08</v>
+        <v>2.11825</v>
       </c>
       <c r="N56" t="n">
         <v>1.104</v>
@@ -3800,7 +3800,7 @@
         <v>1.5445</v>
       </c>
       <c r="M57" t="n">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="N57" t="n">
         <v>1.148</v>
@@ -3859,7 +3859,7 @@
         <v>1.6405</v>
       </c>
       <c r="M58" t="n">
-        <v>2.8405</v>
+        <v>2.80625</v>
       </c>
       <c r="N58" t="n">
         <v>1.163</v>
@@ -3981,7 +3981,7 @@
         <v>58</v>
       </c>
       <c r="M60" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N60" t="n">
         <v>5</v>
@@ -4040,7 +4040,7 @@
         <v>5.992810344827586</v>
       </c>
       <c r="M61" t="n">
-        <v>3.968285714285714</v>
+        <v>4.1325</v>
       </c>
       <c r="N61" t="n">
         <v>38.616</v>
@@ -4097,7 +4097,7 @@
         <v>1.351419870045673</v>
       </c>
       <c r="M62" t="n">
-        <v>0.4611932762901452</v>
+        <v>0.6309075096353551</v>
       </c>
       <c r="N62" t="n">
         <v>9.237536468128285</v>
@@ -4215,7 +4215,7 @@
         <v>5.12825</v>
       </c>
       <c r="M64" t="n">
-        <v>3.7315</v>
+        <v>3.87325</v>
       </c>
       <c r="N64" t="n">
         <v>39.39</v>
@@ -4274,7 +4274,7 @@
         <v>5.7745</v>
       </c>
       <c r="M65" t="n">
-        <v>4.022</v>
+        <v>4.0425</v>
       </c>
       <c r="N65" t="n">
         <v>39.53</v>
@@ -4333,7 +4333,7 @@
         <v>6.58</v>
       </c>
       <c r="M66" t="n">
-        <v>4.234999999999999</v>
+        <v>4.4405</v>
       </c>
       <c r="N66" t="n">
         <v>43.54</v>
@@ -4392,7 +4392,7 @@
         <v>9.237</v>
       </c>
       <c r="M67" t="n">
-        <v>4.541</v>
+        <v>5.282</v>
       </c>
       <c r="N67" t="n">
         <v>47.43</v>
@@ -4455,7 +4455,7 @@
         <v>58</v>
       </c>
       <c r="M68" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N68" t="n">
         <v>5</v>
@@ -4514,7 +4514,7 @@
         <v>0.08984155172413794</v>
       </c>
       <c r="M69" t="n">
-        <v>0.4708142857142857</v>
+        <v>0.4886</v>
       </c>
       <c r="N69" t="n">
         <v>0.018288</v>
@@ -4571,7 +4571,7 @@
         <v>0.02715465426823001</v>
       </c>
       <c r="M70" t="n">
-        <v>0.3245063246870618</v>
+        <v>0.3046170195038823</v>
       </c>
       <c r="N70" t="n">
         <v>0.006033305064390495</v>
@@ -4689,7 +4689,7 @@
         <v>0.0675225</v>
       </c>
       <c r="M72" t="n">
-        <v>0.20875</v>
+        <v>0.226375</v>
       </c>
       <c r="N72" t="n">
         <v>0.01455</v>
@@ -4748,7 +4748,7 @@
         <v>0.091805</v>
       </c>
       <c r="M73" t="n">
-        <v>0.3881</v>
+        <v>0.5005999999999999</v>
       </c>
       <c r="N73" t="n">
         <v>0.01788</v>
@@ -4807,7 +4807,7 @@
         <v>0.103825</v>
       </c>
       <c r="M74" t="n">
-        <v>0.6780999999999999</v>
+        <v>0.6515</v>
       </c>
       <c r="N74" t="n">
         <v>0.01896</v>
@@ -4929,7 +4929,7 @@
         <v>58</v>
       </c>
       <c r="M76" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N76" t="n">
         <v>5</v>
@@ -4988,7 +4988,7 @@
         <v>0.2461844827586207</v>
       </c>
       <c r="M77" t="n">
-        <v>0.1095242857142857</v>
+        <v>0.11227125</v>
       </c>
       <c r="N77" t="n">
         <v>0.69878</v>
@@ -5045,7 +5045,7 @@
         <v>0.08089951272102754</v>
       </c>
       <c r="M78" t="n">
-        <v>0.1646069812064627</v>
+        <v>0.1525943806714389</v>
       </c>
       <c r="N78" t="n">
         <v>0.161203247485899</v>
@@ -5163,7 +5163,7 @@
         <v>0.192025</v>
       </c>
       <c r="M80" t="n">
-        <v>0.005755</v>
+        <v>0.0086325</v>
       </c>
       <c r="N80" t="n">
         <v>0.6151</v>
@@ -5222,7 +5222,7 @@
         <v>0.24455</v>
       </c>
       <c r="M81" t="n">
-        <v>0.01356</v>
+        <v>0.06018</v>
       </c>
       <c r="N81" t="n">
         <v>0.6343</v>
@@ -5281,7 +5281,7 @@
         <v>0.295875</v>
       </c>
       <c r="M82" t="n">
-        <v>0.14755</v>
+        <v>0.1457</v>
       </c>
       <c r="N82" t="n">
         <v>0.7989000000000001</v>
@@ -5403,7 +5403,7 @@
         <v>58</v>
       </c>
       <c r="M84" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N84" t="n">
         <v>5</v>
@@ -5462,7 +5462,7 @@
         <v>0.1453808620689655</v>
       </c>
       <c r="M85" t="n">
-        <v>0.4597857142857143</v>
+        <v>0.4494</v>
       </c>
       <c r="N85" t="n">
         <v>0.05098</v>
@@ -5519,7 +5519,7 @@
         <v>0.03752646707089206</v>
       </c>
       <c r="M86" t="n">
-        <v>0.3224819603666301</v>
+        <v>0.3000019095177324</v>
       </c>
       <c r="N86" t="n">
         <v>0.0101939884245569</v>
@@ -5637,7 +5637,7 @@
         <v>0.11515</v>
       </c>
       <c r="M88" t="n">
-        <v>0.1866</v>
+        <v>0.20315</v>
       </c>
       <c r="N88" t="n">
         <v>0.04712</v>
@@ -5696,7 +5696,7 @@
         <v>0.14795</v>
       </c>
       <c r="M89" t="n">
-        <v>0.4303</v>
+        <v>0.4035</v>
       </c>
       <c r="N89" t="n">
         <v>0.04911</v>
@@ -5755,7 +5755,7 @@
         <v>0.171175</v>
       </c>
       <c r="M90" t="n">
-        <v>0.64175</v>
+        <v>0.614775</v>
       </c>
       <c r="N90" t="n">
         <v>0.04981</v>
